--- a/data/trans_dic/IP12_R1_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP12_R1_2023-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por dolor 2023</t>
+          <t>Menores que limitaron su actividad por dolor 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -538,7 +539,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -571,12 +572,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,94</t>
+          <t>0,0; 6,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -588,7 +589,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -621,24 +622,24 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 5,26</t>
+          <t>0,29; 5,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 6,76</t>
+          <t>0,89; 6,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,51</t>
+          <t>0,95; 4,51</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,02; 9,65</t>
+          <t>1,01; 9,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,51</t>
+          <t>0,0; 4,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,61</t>
+          <t>0,49; 5,03</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,48</t>
+          <t>0,0; 9,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,26</t>
+          <t>0,0; 8,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 6,66</t>
+          <t>0,68; 6,6</t>
         </is>
       </c>
     </row>
@@ -771,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,25; 10,62</t>
+          <t>1,23; 10,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,69; 6,19</t>
+          <t>0,67; 6,05</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -821,24 +822,24 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,36</t>
+          <t>0,0; 11,71</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,44</t>
+          <t>0,0; 7,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,69; 5,72</t>
+          <t>0,68; 5,81</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -871,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,83; 7,63</t>
+          <t>1,93; 7,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,71; 6,11</t>
+          <t>0,77; 5,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,85; 5,98</t>
+          <t>1,78; 5,76</t>
         </is>
       </c>
     </row>
@@ -921,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,11</t>
+          <t>0,0; 2,41</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,2</t>
+          <t>0,0; 2,76</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,15; 2,08</t>
+          <t>0,15; 1,76</t>
         </is>
       </c>
     </row>
@@ -971,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,39; 3,34</t>
+          <t>1,39; 3,33</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,11; 2,82</t>
+          <t>1,08; 2,83</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,42; 2,67</t>
+          <t>1,42; 2,69</t>
         </is>
       </c>
     </row>
@@ -1007,4 +1008,750 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que limitaron su actividad por dolor 2023 (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1294</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1294</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4412</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4404</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2088</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3346</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5434</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>368; 6390</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1137; 8908</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2413; 11486</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1930</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2479</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>591; 5305</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2847</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>618; 6307</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1979</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2129</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4108</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 6473</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 6974</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1008; 9780</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1644</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1644</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>503; 4342</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>506; 4554</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>1390</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1070</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2460</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>0; 5405</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3936</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>698; 5943</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>5153</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>3962</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>9116</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>2399; 9601</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>1201; 9007</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>4993; 16150</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>887</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>868</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>1755</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3179</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4327</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>436; 5077</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>14721</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>13568</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>28290</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>9220; 22171</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>8264; 21555</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>20251; 38405</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12_R1_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP12_R1_2023-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por dolor 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores que en las últimas 2 semanas limitaron su actividad por dolor (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,7 +572,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,02</t>
+          <t>0,0; 6,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,88</t>
+          <t>0,0; 2,83</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 5,04</t>
+          <t>0,0; 4,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,89; 6,98</t>
+          <t>0,78; 6,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 4,51</t>
+          <t>0,93; 4,53</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 9,1</t>
+          <t>0,99; 8,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,24</t>
+          <t>0,0; 4,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 5,03</t>
+          <t>0,49; 4,81</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,23</t>
+          <t>0,0; 8,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,93</t>
+          <t>0,0; 9,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 6,6</t>
+          <t>0,66; 6,02</t>
         </is>
       </c>
     </row>
@@ -777,12 +777,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,23; 10,66</t>
+          <t>1,27; 11,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,67; 6,05</t>
+          <t>0,66; 5,98</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,71</t>
+          <t>0,0; 10,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,0</t>
+          <t>0,0; 6,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,68; 5,81</t>
+          <t>0,67; 5,6</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,93; 7,71</t>
+          <t>1,83; 7,92</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,77; 5,77</t>
+          <t>0,7; 6,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,78; 5,76</t>
+          <t>1,79; 5,57</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,41</t>
+          <t>0,0; 2,03</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,76</t>
+          <t>0,0; 3,39</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,76</t>
+          <t>0,15; 1,84</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,39; 3,33</t>
+          <t>1,43; 3,28</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,08; 2,83</t>
+          <t>1,03; 2,85</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,42; 2,69</t>
+          <t>1,42; 2,68</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por dolor 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores que en las últimas 2 semanas limitaron su actividad por dolor (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4412</t>
+          <t>0; 4545</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4404</t>
+          <t>0; 4323</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>368; 6390</t>
+          <t>0; 5742</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1137; 8908</t>
+          <t>998; 8508</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2413; 11486</t>
+          <t>2364; 11514</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>591; 5305</t>
+          <t>577; 5047</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2847</t>
+          <t>0; 2801</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>618; 6307</t>
+          <t>608; 6031</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 6473</t>
+          <t>0; 5992</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 6974</t>
+          <t>0; 7380</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1008; 9780</t>
+          <t>980; 8932</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>503; 4342</t>
+          <t>515; 4573</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>506; 4554</t>
+          <t>499; 4501</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 5405</t>
+          <t>0; 4784</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3936</t>
+          <t>0; 3852</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>698; 5943</t>
+          <t>688; 5731</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2399; 9601</t>
+          <t>2275; 9858</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1201; 9007</t>
+          <t>1096; 9409</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4993; 16150</t>
+          <t>5011; 15639</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 3179</t>
+          <t>0; 2667</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 4327</t>
+          <t>0; 5315</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>436; 5077</t>
+          <t>438; 5314</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>9220; 22171</t>
+          <t>9523; 21824</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>8264; 21555</t>
+          <t>7886; 21745</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>20251; 38405</t>
+          <t>20271; 38237</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12_R1_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP12_R1_2023-Provincia-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 6,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,83</t>
+          <t>0,0; 3,35</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,53</t>
+          <t>0,92; 6,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,78; 6,67</t>
+          <t>0,52; 6,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,93; 4,53</t>
+          <t>1,11; 4,85</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,99; 8,66</t>
+          <t>0,0; 4,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,17</t>
+          <t>1,06; 9,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,81</t>
+          <t>0,53; 4,66</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,54</t>
+          <t>0,0; 10,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,45</t>
+          <t>0,0; 9,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,66; 6,02</t>
+          <t>0,73; 6,91</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>4,18%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>4,04%</t>
-        </is>
-      </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1,31; 10,52</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>1,27; 11,23</t>
-        </is>
-      </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,66; 5,98</t>
+          <t>0,7; 6,05</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,36</t>
+          <t>0,0; 6,64</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,86</t>
+          <t>0,0; 9,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,67; 5,6</t>
+          <t>0,7; 6,26</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,83; 7,92</t>
+          <t>0,94; 6,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,7; 6,03</t>
+          <t>1,84; 7,99</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,79; 5,57</t>
+          <t>1,98; 6,63</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,03</t>
+          <t>0,0; 3,41</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,39</t>
+          <t>0,0; 1,72</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,84</t>
+          <t>0,13; 2,06</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,43; 3,28</t>
+          <t>1,14; 2,95</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,03; 2,85</t>
+          <t>1,5; 3,56</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,42; 2,68</t>
+          <t>1,49; 2,84</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1172</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4545</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3899</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4323</t>
+          <t>0; 4038</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2088</t>
+          <t>2973</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3346</t>
+          <t>2159</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>5132</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5742</t>
+          <t>1067; 7990</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>998; 8508</t>
+          <t>524; 6736</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2364; 11514</t>
+          <t>2396; 10491</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1930</t>
+          <t>455</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1911</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2479</t>
+          <t>2366</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>577; 5047</t>
+          <t>0; 2560</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2801</t>
+          <t>598; 5573</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>608; 6031</t>
+          <t>616; 5400</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>2109</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2129</t>
+          <t>2077</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4108</t>
+          <t>4185</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 5992</t>
+          <t>0; 7362</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 7380</t>
+          <t>0; 6378</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>980; 8932</t>
+          <t>1049; 9881</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1654</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>1644</t>
-        </is>
-      </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1644</t>
+          <t>1654</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>519; 4162</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>515; 4573</t>
-        </is>
-      </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>499; 4501</t>
+          <t>530; 4546</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1390</t>
+          <t>893</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>1445</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2460</t>
+          <t>2339</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4784</t>
+          <t>0; 3250</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3852</t>
+          <t>0; 4468</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>688; 5731</t>
+          <t>664; 5930</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>5153</t>
+          <t>4092</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3962</t>
+          <t>5125</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9116</t>
+          <t>9217</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2275; 9858</t>
+          <t>1331; 9657</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1096; 9409</t>
+          <t>2254; 9788</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5011; 15639</t>
+          <t>5214; 17484</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>950</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>770</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1755</t>
+          <t>1719</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 2667</t>
+          <t>0; 5436</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 5315</t>
+          <t>0; 2410</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>438; 5314</t>
+          <t>384; 6190</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>23</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>14721</t>
+          <t>13127</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>13568</t>
+          <t>14659</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>28290</t>
+          <t>27785</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>9523; 21824</t>
+          <t>7972; 20665</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>7886; 21745</t>
+          <t>9434; 22381</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>20271; 38237</t>
+          <t>19773; 37784</t>
         </is>
       </c>
     </row>
